--- a/df_list_20260306.xlsx
+++ b/df_list_20260306.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-06 09:58:34</t>
+          <t>2026-03-06 23:00:46</t>
         </is>
       </c>
     </row>
